--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_232_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_232_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9045</v>
+        <v>5.2658</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5348</v>
+        <v>3.9634</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3697</v>
+        <v>1.3025</v>
       </c>
       <c r="G2" t="n">
         <v>2.9063</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2337</v>
+        <v>0.1276</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5228</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2891</v>
+        <v>0.2219</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5162</v>
+        <v>3.9754</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8369</v>
+        <v>3.0609</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6793</v>
+        <v>0.9145</v>
       </c>
       <c r="G3" t="n">
         <v>-1.4473</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0934</v>
+        <v>-0.6341</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4753</v>
+        <v>-0.2513</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6181</v>
+        <v>-0.3828</v>
       </c>
       <c r="V3" t="n">
         <v>5.361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4713</v>
+        <v>2.8561</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6808</v>
+        <v>2.4016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7905</v>
+        <v>0.4545</v>
       </c>
       <c r="G4" t="n">
         <v>1.3999</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2854</v>
+        <v>0.6702</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4876</v>
+        <v>0.2084</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7978</v>
+        <v>0.4617</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5259</v>
+        <v>2.2713</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3968</v>
+        <v>2.3103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.129</v>
+        <v>-0.039</v>
       </c>
       <c r="G5" t="n">
         <v>0.4425</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.525</v>
+        <v>-0.7795</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1098</v>
+        <v>-0.1964</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4151</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>2.1444</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.9719</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1056</v>
+        <v>1.2117</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5759</v>
+        <v>-0.2398</v>
       </c>
       <c r="G6" t="n">
         <v>0.6458</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9357</v>
+        <v>-0.4935</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2513</v>
+        <v>-0.1452</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6844</v>
+        <v>-0.3484</v>
       </c>
       <c r="V6" t="n">
         <v>0.8197</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0776</v>
+        <v>-0.0649</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7198</v>
+        <v>-1.539</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6421</v>
+        <v>1.4741</v>
       </c>
       <c r="G7" t="n">
         <v>1.4526</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5329</v>
+        <v>-0.5201</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.55</v>
+        <v>-0.3692</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0171</v>
+        <v>-0.1509</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1539</v>
+        <v>-0.1129</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3784</v>
+        <v>0.4531</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5324</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.3195</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1349</v>
+        <v>0.1759</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2161</v>
+        <v>-0.1415</v>
       </c>
       <c r="U8" t="n">
-        <v>0.351</v>
+        <v>0.3174</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2583</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4122</v>
+        <v>-0.884</v>
       </c>
       <c r="F9" t="n">
-        <v>0.154</v>
+        <v>0.322</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3218</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3677</v>
+        <v>0.0639</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4129</v>
+        <v>-0.0589</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0913</v>
+        <v>-1.0063</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7051</v>
+        <v>-1.3512</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6138</v>
+        <v>0.3449</v>
       </c>
       <c r="G10" t="n">
         <v>0.5296999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0053</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U10" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9304</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3183</v>
+        <v>-1.4379</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7047</v>
+        <v>-2.9657</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3864</v>
+        <v>1.5278</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3551</v>
+        <v>-2.8337</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8295</v>
+        <v>-1.5689</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1845</v>
+        <v>-1.2648</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2122</v>
+        <v>-2.3796</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4502</v>
+        <v>-0.1275</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6625</v>
+        <v>-2.2521</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428</v>
+        <v>-0.4541</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3792</v>
+        <v>-1.4414</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5221</v>
+        <v>0.9873</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5316</v>
+        <v>-1.0528</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5975</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0659</v>
+        <v>-0.3376</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.214</v>
+        <v>2.6805</v>
       </c>
       <c r="W11" t="n">
+        <v>2.6805</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-1.214</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3765</v>
+        <v>-1.9912</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7363</v>
+        <v>-2.5121</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3598</v>
+        <v>0.5209</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8337</v>
+        <v>0.3551</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5689</v>
+        <v>-0.8295</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2648</v>
+        <v>1.1845</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3796</v>
+        <v>0.2122</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1275</v>
+        <v>-0.4502</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2521</v>
+        <v>0.6625</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4541</v>
+        <v>0.1428</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4414</v>
+        <v>-0.3792</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9873</v>
+        <v>0.5221</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9913</v>
+        <v>-0.2045</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4857</v>
+        <v>-0.4048</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5056</v>
+        <v>0.2003</v>
       </c>
       <c r="V12" t="n">
-        <v>2.6805</v>
+        <v>-1.214</v>
       </c>
       <c r="W12" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.671699999999998</v>
+        <v>10.1653</v>
       </c>
       <c r="E13" t="n">
-        <v>2.655200000000002</v>
+        <v>4.148999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>6.016299999999999</v>
+        <v>6.0164</v>
       </c>
       <c r="G13" t="n">
         <v>2.4486</v>
@@ -1441,7 +1441,7 @@
         <v>5.755599999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>7.363899999999999</v>
+        <v>7.3639</v>
       </c>
       <c r="K13" t="n">
         <v>4.955799999999999</v>
@@ -1468,16 +1468,16 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.0503</v>
+        <v>-2.5566</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.8308</v>
+        <v>-2.3372</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2195000000000001</v>
+        <v>-0.2196</v>
       </c>
       <c r="V13" t="n">
-        <v>9.113700000000001</v>
+        <v>9.1137</v>
       </c>
       <c r="W13" t="n">
         <v>13.0393</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1917</v>
+        <v>4.2247</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1042</v>
+        <v>2.7068</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0875</v>
+        <v>1.5179</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8515</v>
+        <v>1.6979</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6264999999999999</v>
+        <v>2.7586</v>
       </c>
       <c r="I14" t="n">
-        <v>2.225</v>
+        <v>-1.0607</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1099</v>
+        <v>0.7795</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7211</v>
+        <v>2.2049</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3888</v>
+        <v>-1.4255</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2583</v>
+        <v>0.9184</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0945</v>
+        <v>0.5536</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1638</v>
+        <v>0.3648</v>
       </c>
       <c r="P14" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9665</v>
+        <v>1.2975</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2442</v>
+        <v>0.4092</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7222</v>
+        <v>0.8883</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4447</v>
+        <v>3.9901</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3529</v>
+        <v>3.1042</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0917</v>
+        <v>0.8859</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6979</v>
+        <v>2.8515</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7586</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0607</v>
+        <v>2.225</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7795</v>
+        <v>4.1099</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2049</v>
+        <v>1.7211</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4255</v>
+        <v>2.3888</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9184</v>
+        <v>-1.2583</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5536</v>
+        <v>-1.0945</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3648</v>
+        <v>-0.1638</v>
       </c>
       <c r="P15" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S15" t="n">
-        <v>0.5175</v>
+        <v>0.7648</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0553</v>
+        <v>0.2442</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4621</v>
+        <v>0.5206</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9632</v>
+        <v>1.9155</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2644</v>
+        <v>0.8296</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3012</v>
+        <v>1.0859</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6291</v>
+        <v>2.1748</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4021</v>
+        <v>0.599</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.773</v>
+        <v>1.5758</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7373</v>
+        <v>2.2248</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4535</v>
+        <v>0.696</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7163</v>
+        <v>1.5289</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1082</v>
+        <v>-0.05</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0514</v>
+        <v>-0.097</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0568</v>
+        <v>0.047</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6383</v>
+        <v>0.581</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7591</v>
+        <v>-0.0035</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1208</v>
+        <v>0.5845</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.32</v>
+        <v>1.7939</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3578</v>
+        <v>1.7926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.0013</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1748</v>
+        <v>0.6291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.599</v>
+        <v>1.4021</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5758</v>
+        <v>-0.773</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2248</v>
+        <v>1.7373</v>
       </c>
       <c r="K17" t="n">
-        <v>0.696</v>
+        <v>2.4535</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5289</v>
+        <v>-0.7163</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.05</v>
+        <v>-1.1082</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.097</v>
+        <v>-1.0514</v>
       </c>
       <c r="O17" t="n">
-        <v>0.047</v>
+        <v>-0.0568</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0145</v>
+        <v>0.4689</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4753</v>
+        <v>0.2873</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4608</v>
+        <v>0.1817</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4093</v>
+        <v>0.793</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.413</v>
+        <v>-1.2335</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0037</v>
+        <v>2.0265</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1906</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5614</v>
+        <v>0.6409</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1123</v>
+        <v>0.0672</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5737</v>
       </c>
       <c r="V18" t="n">
         <v>1.1829</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1678</v>
+        <v>-1.1178</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9774</v>
+        <v>-1.0954</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1904</v>
+        <v>-0.0224</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5484</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.293</v>
+        <v>0.3431</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4208</v>
+        <v>0.3029</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1278</v>
+        <v>0.0402</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7941</v>
+        <v>-1.8904</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.032</v>
+        <v>-1.3555</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.762</v>
+        <v>-0.5349</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7097</v>
+        <v>-0.0044</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0336</v>
+        <v>0.7083</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7433</v>
+        <v>-0.7127</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.338</v>
+        <v>0.21</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8739</v>
+        <v>0.605</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.2118</v>
+        <v>-0.3949</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3717</v>
+        <v>-0.2144</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8401999999999999</v>
+        <v>0.1034</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4685</v>
+        <v>-0.3178</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6657</v>
+        <v>0.3459</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3239</v>
+        <v>-0.3183</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3418</v>
+        <v>0.6642</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.428</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8593</v>
+        <v>-2.0952</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.012</v>
+        <v>-1.2479</v>
       </c>
       <c r="F21" t="n">
         <v>-0.8473000000000001</v>
@@ -2092,10 +2092,10 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3224</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1019</v>
+        <v>-0.3378</v>
       </c>
       <c r="U21" t="n">
         <v>0.4244</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1327</v>
+        <v>-3.6406</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7094</v>
+        <v>-0.9597</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4233</v>
+        <v>-2.6809</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0044</v>
+        <v>-1.2032</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7083</v>
+        <v>0.0013</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7127</v>
+        <v>-1.2045</v>
       </c>
       <c r="J22" t="n">
-        <v>0.21</v>
+        <v>0.6482</v>
       </c>
       <c r="K22" t="n">
-        <v>0.605</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3949</v>
+        <v>0.1104</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2144</v>
+        <v>-1.8514</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1034</v>
+        <v>-0.5365</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3178</v>
+        <v>-1.3149</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.9278</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1037</v>
+        <v>-0.4373</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6721</v>
+        <v>-0.4481</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7758</v>
+        <v>0.0108</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7414</v>
+        <v>-3.686</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9597</v>
+        <v>-2.5081</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7817</v>
+        <v>-1.178</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2032</v>
+        <v>-1.0882</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0013</v>
+        <v>-2.3026</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2045</v>
+        <v>1.2144</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6482</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5377999999999999</v>
+        <v>-1.2296</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1104</v>
+        <v>2.0073</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8514</v>
+        <v>-1.8659</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5365</v>
+        <v>-1.073</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3149</v>
+        <v>-0.7929</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5381</v>
+        <v>0.2783</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4481</v>
+        <v>-0.0901</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0901</v>
+        <v>0.3684</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X23" t="n">
         <v>-1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8883</v>
+        <v>-3.8994</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.744</v>
+        <v>-1.8013</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1444</v>
+        <v>-2.0981</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0882</v>
+        <v>-1.7097</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3026</v>
+        <v>0.0336</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2144</v>
+        <v>-1.7433</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7776999999999999</v>
+        <v>-1.338</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2296</v>
+        <v>0.8739</v>
       </c>
       <c r="L24" t="n">
-        <v>2.0073</v>
+        <v>-2.2118</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8659</v>
+        <v>-0.3717</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.073</v>
+        <v>-0.8401999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7929</v>
+        <v>0.4685</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>0.076</v>
+        <v>0.5603</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.326</v>
+        <v>0.5546</v>
       </c>
       <c r="U24" t="n">
-        <v>0.402</v>
+        <v>0.0057</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7886</v>
+        <v>-2.2862</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2836</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5984</v>
+        <v>-4.2731</v>
       </c>
       <c r="E25" t="n">
         <v>-3.7121</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8863</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7158</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4187</v>
+        <v>-0.0934</v>
       </c>
       <c r="T25" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0294</v>
+        <v>0.3547</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6083</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.671700000000001</v>
+        <v>-7.8853</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.480300000000001</v>
+        <v>-5.4803</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1915</v>
+        <v>-2.4051</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.4485</v>
+        <v>-2.448499999999999</v>
       </c>
       <c r="H26" t="n">
         <v>3.3071</v>
@@ -2458,16 +2458,16 @@
         <v>4.9153</v>
       </c>
       <c r="K26" t="n">
-        <v>8.263100000000001</v>
+        <v>8.2631</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.347600000000002</v>
+        <v>-3.347600000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-7.3637</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.955699999999999</v>
+        <v>-4.9557</v>
       </c>
       <c r="O26" t="n">
         <v>-2.4081</v>
@@ -2482,16 +2482,16 @@
         <v>13.9174</v>
       </c>
       <c r="S26" t="n">
-        <v>4.0504</v>
+        <v>4.8365</v>
       </c>
       <c r="T26" t="n">
         <v>0.2195</v>
       </c>
       <c r="U26" t="n">
-        <v>3.8307</v>
+        <v>4.6172</v>
       </c>
       <c r="V26" t="n">
-        <v>-9.113700000000001</v>
+        <v>-9.1137</v>
       </c>
       <c r="W26" t="n">
         <v>4.4617</v>
